--- a/artfynd/A 56995-2024 artfynd.xlsx
+++ b/artfynd/A 56995-2024 artfynd.xlsx
@@ -775,7 +775,7 @@
         <v>124838791</v>
       </c>
       <c r="B3" t="n">
-        <v>57881</v>
+        <v>57632</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 56995-2024 artfynd.xlsx
+++ b/artfynd/A 56995-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124838028</v>
+        <v>124838189</v>
       </c>
       <c r="B2" t="n">
-        <v>105205</v>
+        <v>57950</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,37 +686,41 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221141</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Brunnsholm, Brunnsholm, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>555520</v>
+        <v>555532</v>
       </c>
       <c r="R2" t="n">
-        <v>6342879</v>
+        <v>6342860</v>
       </c>
       <c r="S2" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -775,11 +779,11 @@
         <v>124838791</v>
       </c>
       <c r="B3" t="n">
-        <v>57632</v>
+        <v>57950</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -874,10 +878,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124836304</v>
+        <v>124836315</v>
       </c>
       <c r="B4" t="n">
-        <v>100451</v>
+        <v>106156</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -885,21 +889,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222498</v>
+        <v>221141</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -909,10 +913,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>555590</v>
+        <v>555588</v>
       </c>
       <c r="R4" t="n">
-        <v>6342883</v>
+        <v>6342890</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -974,7 +978,7 @@
         <v>124837739</v>
       </c>
       <c r="B5" t="n">
-        <v>105205</v>
+        <v>106156</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1068,10 +1072,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124836048</v>
+        <v>124838028</v>
       </c>
       <c r="B6" t="n">
-        <v>100451</v>
+        <v>106156</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1079,21 +1083,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222498</v>
+        <v>221141</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1103,13 +1107,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>555570</v>
+        <v>555520</v>
       </c>
       <c r="R6" t="n">
-        <v>6342818</v>
+        <v>6342879</v>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1165,10 +1169,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124836315</v>
+        <v>124838163</v>
       </c>
       <c r="B7" t="n">
-        <v>105205</v>
+        <v>106156</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1200,10 +1204,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>555588</v>
+        <v>555517</v>
       </c>
       <c r="R7" t="n">
-        <v>6342890</v>
+        <v>6342879</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>
@@ -1262,10 +1266,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124838163</v>
+        <v>124836431</v>
       </c>
       <c r="B8" t="n">
-        <v>105205</v>
+        <v>103683</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1273,16 +1277,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221141</v>
+        <v>222002</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Underviol</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Viola mirabilis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1297,10 +1301,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>555517</v>
+        <v>555577</v>
       </c>
       <c r="R8" t="n">
-        <v>6342879</v>
+        <v>6342895</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1359,52 +1363,48 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124838189</v>
+        <v>124836048</v>
       </c>
       <c r="B9" t="n">
-        <v>57632</v>
+        <v>101326</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Brunnsholm, Brunnsholm, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>555532</v>
+        <v>555570</v>
       </c>
       <c r="R9" t="n">
-        <v>6342860</v>
+        <v>6342818</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1460,10 +1460,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124836431</v>
+        <v>124836304</v>
       </c>
       <c r="B10" t="n">
-        <v>102771</v>
+        <v>101326</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1471,21 +1471,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>222002</v>
+        <v>222498</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Underviol</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Viola mirabilis</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1495,10 +1495,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>555577</v>
+        <v>555590</v>
       </c>
       <c r="R10" t="n">
-        <v>6342895</v>
+        <v>6342883</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>

--- a/artfynd/A 56995-2024 artfynd.xlsx
+++ b/artfynd/A 56995-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124838189</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -875,6 +885,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124838791</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -972,6 +987,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124836315</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1069,6 +1089,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124837739</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1166,6 +1191,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124838028</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1263,6 +1293,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124838163</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1360,6 +1395,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124836431</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1457,6 +1497,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124836048</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1554,8 +1599,24 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124836304</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>